--- a/artfynd/A 17466-2026 artfynd.xlsx
+++ b/artfynd/A 17466-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133194979</v>
       </c>
       <c r="B2" t="n">
-        <v>96712</v>
+        <v>96715</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133194061</v>
       </c>
       <c r="B3" t="n">
-        <v>91934</v>
+        <v>91937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17466-2026 artfynd.xlsx
+++ b/artfynd/A 17466-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>133194979</v>
       </c>
       <c r="B2" t="n">
-        <v>96715</v>
+        <v>96716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133194061</v>
       </c>
       <c r="B3" t="n">
-        <v>91937</v>
+        <v>91938</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -964,6 +964,223 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133374120</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Söder om Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>567580</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6505670</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133374376</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Söder om Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>567688</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6505561</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På mycket gammal gran</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17466-2026 artfynd.xlsx
+++ b/artfynd/A 17466-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133194979</v>
       </c>
       <c r="B2" t="n">
-        <v>96716</v>
+        <v>96718</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133194061</v>
       </c>
       <c r="B3" t="n">
-        <v>91938</v>
+        <v>91939</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>133374120</v>
       </c>
       <c r="B5" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17466-2026 artfynd.xlsx
+++ b/artfynd/A 17466-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133194979</v>
       </c>
       <c r="B2" t="n">
-        <v>96756</v>
+        <v>96783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133194061</v>
       </c>
       <c r="B3" t="n">
-        <v>91968</v>
+        <v>91995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133193861</v>
+        <v>133374120</v>
       </c>
       <c r="B4" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +880,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjuvklint, Tjuvklint, Ög</t>
+          <t>Söder om Södra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567594</v>
+        <v>567580</v>
       </c>
       <c r="R4" t="n">
-        <v>6505638</v>
+        <v>6505670</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,52 +962,53 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133374120</v>
+        <v>133374376</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>4782</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1009,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567580</v>
+        <v>567688</v>
       </c>
       <c r="R5" t="n">
-        <v>6505670</v>
+        <v>6505561</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,12 +1056,18 @@
           <t>2026-05-07</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På mycket gammal gran</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1071,10 +1086,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133374376</v>
+        <v>133193861</v>
       </c>
       <c r="B6" t="n">
-        <v>4782</v>
+        <v>8460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,46 +1097,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Söder om Södra Granstorp, Ög</t>
+          <t>Tjuvklint, Tjuvklint, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567688</v>
+        <v>567594</v>
       </c>
       <c r="R6" t="n">
-        <v>6505561</v>
+        <v>6505638</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,30 +1159,24 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På mycket gammal gran</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 17466-2026 artfynd.xlsx
+++ b/artfynd/A 17466-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133194979</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133194061</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133374120</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133374376</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,8 +1205,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133193861</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 17466-2026 artfynd.xlsx
+++ b/artfynd/A 17466-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133194979</v>
+        <v>136297043</v>
       </c>
       <c r="B2" t="n">
-        <v>96783</v>
+        <v>96780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567673</v>
+        <v>567596</v>
       </c>
       <c r="R2" t="n">
-        <v>6505502</v>
+        <v>6505631</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,38 +776,38 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133194979</t>
+          <t>https://artportalen.se/Sighting/136297043</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133194061</v>
+        <v>133194979</v>
       </c>
       <c r="B3" t="n">
-        <v>91995</v>
+        <v>96783</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567659</v>
+        <v>567673</v>
       </c>
       <c r="R3" t="n">
-        <v>6505612</v>
+        <v>6505502</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -878,62 +878,54 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133194061</t>
+          <t>https://artportalen.se/Sighting/133194979</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133374120</v>
+        <v>133194061</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>91995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söder om Södra Granstorp, Ög</t>
+          <t>Tjuvklint, Tjuvklint, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567580</v>
+        <v>567659</v>
       </c>
       <c r="R4" t="n">
-        <v>6505670</v>
+        <v>6505612</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,74 +969,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133374120</t>
+          <t>https://artportalen.se/Sighting/133194061</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133374376</v>
+        <v>136295685</v>
       </c>
       <c r="B5" t="n">
-        <v>4782</v>
+        <v>92094</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söder om Södra Granstorp, Ög</t>
+          <t>Södra Granstorp, Södra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567688</v>
+        <v>567559</v>
       </c>
       <c r="R5" t="n">
-        <v>6505561</v>
+        <v>6505786</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,17 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På mycket gammal gran</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,56 +1065,55 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133374376</t>
+          <t>https://artportalen.se/Sighting/136295685</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133193861</v>
+        <v>136295919</v>
       </c>
       <c r="B6" t="n">
-        <v>8460</v>
+        <v>80068</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567594</v>
+        <v>567631</v>
       </c>
       <c r="R6" t="n">
-        <v>6505638</v>
+        <v>6505684</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1176,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,7 +1184,647 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136295919</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133374120</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Söder om Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>567580</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6505670</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133374120</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136296227</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tjuvklint, Tjuvklint, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>567672</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6505595</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136296227</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133374376</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4782</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Söder om Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>567688</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6505561</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På mycket gammal gran</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133374376</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136296105</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tjuvklint, Tjuvklint, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>567666</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6505600</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136296105</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133193861</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tjuvklint, Tjuvklint, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>567594</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6505638</v>
+      </c>
+      <c r="S11" t="n">
+        <v>13</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/133193861</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136297068</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tjuvklint, Tjuvklint, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>567596</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6505631</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136297068</t>
         </is>
       </c>
     </row>
@@ -1218,6 +1835,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17466-2026 artfynd.xlsx
+++ b/artfynd/A 17466-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136297043</v>
       </c>
       <c r="B2" t="n">
-        <v>96780</v>
+        <v>96781</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136295685</v>
       </c>
       <c r="B5" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136295919</v>
       </c>
       <c r="B6" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136296105</v>
       </c>
       <c r="B10" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
